--- a/izlaz/PENZIONERI_DRVA.xlsx
+++ b/izlaz/PENZIONERI_DRVA.xlsx
@@ -542,10 +542,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
@@ -629,10 +627,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>319</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -712,10 +708,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>177</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -795,10 +789,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
+      <c r="B5" s="2" t="n">
+        <v>224</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -878,10 +870,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+      <c r="B6" s="2" t="n">
+        <v>249</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -961,10 +951,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="B7" s="2" t="n">
+        <v>58</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -1044,10 +1032,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="B8" s="1" t="n">
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
@@ -1135,10 +1121,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+      <c r="B9" s="2" t="n">
+        <v>219</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1218,10 +1202,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="B10" s="1" t="n">
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
@@ -1309,10 +1291,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
+      <c r="B11" s="1" t="n">
+        <v>195</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -1400,10 +1380,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
+      <c r="B12" s="2" t="n">
+        <v>309</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1483,10 +1461,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
+      <c r="B13" s="2" t="n">
+        <v>343</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1566,10 +1542,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
+      <c r="B14" s="1" t="n">
+        <v>263</v>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
@@ -1657,10 +1631,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="B15" s="2" t="n">
+        <v>96</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1740,10 +1712,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="B16" s="2" t="n">
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1823,10 +1793,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="B17" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1906,10 +1874,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
+      <c r="B18" s="1" t="n">
+        <v>202</v>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
@@ -1997,10 +1963,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="B19" s="1" t="n">
+        <v>162</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
@@ -2088,10 +2052,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
+      <c r="B20" s="1" t="n">
+        <v>204</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
@@ -2179,10 +2141,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
+      <c r="B21" s="2" t="n">
+        <v>252</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2222,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
+      <c r="B22" s="1" t="n">
+        <v>255</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
@@ -2353,10 +2311,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
+      <c r="B23" s="1" t="n">
+        <v>348</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
@@ -2440,10 +2396,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
+      <c r="B24" s="2" t="n">
+        <v>274</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -2519,10 +2473,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
+      <c r="B25" s="2" t="n">
+        <v>273</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -2598,10 +2550,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="B26" s="1" t="n">
+        <v>139</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -2689,10 +2639,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="B27" s="1" t="n">
+        <v>110</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -2780,10 +2728,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B28" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
@@ -2871,10 +2817,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="B29" s="1" t="n">
+        <v>138</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -2962,10 +2906,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
+      <c r="B30" s="1" t="n">
+        <v>194</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -3053,10 +2995,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
+      <c r="B31" s="1" t="n">
+        <v>253</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
@@ -3144,10 +3084,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="B32" s="2" t="n">
+        <v>94</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -3227,10 +3165,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
+      <c r="B33" s="1" t="n">
+        <v>238</v>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
@@ -3314,10 +3250,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="B34" s="2" t="n">
+        <v>170</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -3397,10 +3331,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
+      <c r="B35" s="1" t="n">
+        <v>334</v>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
@@ -3484,10 +3416,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="B36" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -3567,10 +3497,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="B37" s="2" t="n">
+        <v>68</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -3650,10 +3578,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+      <c r="B38" s="2" t="n">
+        <v>151</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -3733,10 +3659,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="B39" s="2" t="n">
+        <v>169</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -3816,10 +3740,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
+      <c r="B40" s="1" t="n">
+        <v>267</v>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
@@ -3907,10 +3829,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="B41" s="2" t="n">
+        <v>76</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -3990,10 +3910,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
+      <c r="B42" s="1" t="n">
+        <v>276</v>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
@@ -4081,10 +3999,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
+      <c r="B43" s="1" t="n">
+        <v>285</v>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
@@ -4172,10 +4088,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+      <c r="B44" s="1" t="n">
+        <v>250</v>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
@@ -4263,10 +4177,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="B45" s="1" t="n">
+        <v>99</v>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
@@ -4354,10 +4266,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="B46" s="1" t="n">
+        <v>98</v>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
@@ -4445,10 +4355,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="B47" s="1" t="n">
+        <v>145</v>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
@@ -4536,10 +4444,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
+      <c r="B48" s="2" t="n">
+        <v>311</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -4619,10 +4525,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="B49" s="2" t="n">
+        <v>269</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -4698,10 +4602,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="B50" s="2" t="n">
+        <v>82</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -4781,10 +4683,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="B51" s="2" t="n">
+        <v>83</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -4864,10 +4764,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
+      <c r="B52" s="2" t="n">
+        <v>243</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -4947,10 +4845,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
+      <c r="B53" s="2" t="n">
+        <v>244</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
@@ -5030,10 +4926,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="B54" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
@@ -5113,10 +5007,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="B55" s="2" t="n">
+        <v>34</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -5196,10 +5088,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B56" s="1" t="n">
+        <v>310</v>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
@@ -5287,10 +5177,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
+      <c r="B57" s="2" t="n">
+        <v>295</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -5370,10 +5258,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="B58" s="2" t="n">
+        <v>158</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
@@ -5453,10 +5339,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
+      <c r="B59" s="1" t="n">
+        <v>164</v>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
@@ -5544,10 +5428,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="B60" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
@@ -5627,10 +5509,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
+      <c r="B61" s="2" t="n">
+        <v>216</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
@@ -5706,10 +5586,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
+      <c r="B62" s="2" t="n">
+        <v>333</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
@@ -5789,10 +5667,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="B63" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
@@ -5872,10 +5748,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="B64" s="1" t="n">
+        <v>59</v>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
@@ -5963,10 +5837,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
+      <c r="B65" s="2" t="n">
+        <v>264</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -6046,10 +5918,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
+      <c r="B66" s="1" t="n">
+        <v>303</v>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
@@ -6137,10 +6007,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
+      <c r="B67" s="1" t="n">
+        <v>298</v>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
@@ -6224,10 +6092,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="B68" s="2" t="n">
+        <v>176</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
@@ -6307,10 +6173,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="B69" s="1" t="n">
+        <v>125</v>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
@@ -6394,10 +6258,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="B70" s="2" t="n">
+        <v>262</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
@@ -6477,10 +6339,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
+      <c r="B71" s="2" t="n">
+        <v>286</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
@@ -6556,10 +6416,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="B72" s="1" t="n">
+        <v>72</v>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
@@ -6647,10 +6505,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
+      <c r="B73" s="2" t="n">
+        <v>166</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
@@ -6730,10 +6586,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="B74" s="1" t="n">
+        <v>148</v>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
@@ -6821,10 +6675,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="B75" s="1" t="n">
+        <v>149</v>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
@@ -6912,10 +6764,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="B76" s="2" t="n">
+        <v>106</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
@@ -6995,10 +6845,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="B77" s="2" t="n">
+        <v>107</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
@@ -7078,10 +6926,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
+      <c r="B78" s="2" t="n">
+        <v>296</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -7161,10 +7007,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="B79" s="1" t="n">
+        <v>74</v>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
@@ -7252,10 +7096,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="B80" s="2" t="n">
+        <v>192</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
@@ -7335,10 +7177,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
+      <c r="B81" s="2" t="n">
+        <v>190</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -7418,10 +7258,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+      <c r="B82" s="2" t="n">
+        <v>140</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
@@ -7501,10 +7339,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="B83" s="2" t="n">
+        <v>294</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
@@ -7584,10 +7420,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
+      <c r="B84" s="2" t="n">
+        <v>330</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
@@ -7663,10 +7497,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
+      <c r="B85" s="2" t="n">
+        <v>321</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
@@ -7746,10 +7578,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="B86" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
@@ -7837,10 +7667,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B87" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7748,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B88" s="1" t="n">
+        <v>17</v>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
@@ -8011,10 +7837,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="B89" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
@@ -8094,10 +7918,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="B90" s="2" t="n">
+        <v>132</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
@@ -8177,10 +7999,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="B91" s="2" t="n">
+        <v>84</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
@@ -8260,10 +8080,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="B92" s="1" t="n">
+        <v>77</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
@@ -8351,10 +8169,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
+      <c r="B93" s="1" t="n">
+        <v>317</v>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
@@ -8442,10 +8258,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
+      <c r="B94" s="1" t="n">
+        <v>318</v>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
@@ -8529,10 +8343,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
+      <c r="B95" s="2" t="n">
+        <v>349</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
@@ -8612,10 +8424,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B96" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
@@ -8691,10 +8501,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="B97" s="2" t="n">
+        <v>331</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
@@ -8774,10 +8582,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
+      <c r="B98" s="1" t="n">
+        <v>339</v>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
@@ -8865,10 +8671,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
+      <c r="B99" s="1" t="n">
+        <v>278</v>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
@@ -8956,10 +8760,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="B100" s="1" t="n">
+        <v>143</v>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
@@ -9043,10 +8845,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
+      <c r="B101" s="2" t="n">
+        <v>282</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
@@ -9126,10 +8926,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
+      <c r="B102" s="2" t="n">
+        <v>248</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
@@ -9209,10 +9007,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="B103" s="2" t="n">
+        <v>73</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
@@ -9288,10 +9084,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+      <c r="B104" s="2" t="n">
+        <v>289</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
@@ -9371,10 +9165,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="B105" s="2" t="n">
+        <v>179</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
@@ -9454,10 +9246,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="B106" s="2" t="n">
+        <v>75</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
@@ -9537,10 +9327,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="B107" s="2" t="n">
+        <v>137</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
@@ -9620,10 +9408,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
+      <c r="B108" s="1" t="n">
+        <v>277</v>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
@@ -9711,10 +9497,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
+      <c r="B109" s="2" t="n">
+        <v>223</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
@@ -9794,10 +9578,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
+      <c r="B110" s="2" t="n">
+        <v>332</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
@@ -9877,10 +9659,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="B111" s="2" t="n">
+        <v>168</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
@@ -9960,10 +9740,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="B112" s="2" t="n">
+        <v>167</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
@@ -10043,10 +9821,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
+      <c r="B113" s="2" t="n">
+        <v>207</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
@@ -10126,10 +9902,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
+      <c r="B114" s="2" t="n">
+        <v>342</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
@@ -10209,10 +9983,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
+      <c r="B115" s="2" t="n">
+        <v>291</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
@@ -10292,10 +10064,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
+      <c r="B116" s="1" t="n">
+        <v>218</v>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
@@ -10383,10 +10153,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
+      <c r="B117" s="2" t="n">
+        <v>206</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
@@ -10466,10 +10234,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="B118" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
@@ -10557,10 +10323,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="B119" s="1" t="n">
+        <v>86</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
@@ -10648,10 +10412,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
+      <c r="B120" s="1" t="n">
+        <v>308</v>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
@@ -10739,10 +10501,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
+      <c r="B121" s="1" t="n">
+        <v>171</v>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
@@ -10830,10 +10590,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+      <c r="B122" s="1" t="n">
+        <v>154</v>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
@@ -10921,10 +10679,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
+      <c r="B123" s="1" t="n">
+        <v>338</v>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
@@ -11012,10 +10768,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
+      <c r="B124" s="2" t="n">
+        <v>327</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
@@ -11095,10 +10849,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
+      <c r="B125" s="1" t="n">
+        <v>293</v>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
@@ -11182,10 +10934,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
+      <c r="B126" s="2" t="n">
+        <v>353</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
@@ -11261,10 +11011,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="B127" s="2" t="n">
+        <v>66</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
@@ -11344,10 +11092,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
+      <c r="B128" s="2" t="n">
+        <v>268</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
@@ -11427,10 +11173,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="B129" s="1" t="n">
+        <v>320</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
@@ -11518,10 +11262,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="B130" s="1" t="n">
+        <v>222</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
@@ -11605,10 +11347,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="B131" s="2" t="n">
+        <v>328</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
@@ -11688,10 +11428,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="B132" s="1" t="n">
+        <v>144</v>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
@@ -11779,10 +11517,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="B133" s="1" t="n">
+        <v>91</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
@@ -11866,10 +11602,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="B134" s="1" t="n">
+        <v>62</v>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
@@ -11957,10 +11691,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="B135" s="1" t="n">
+        <v>188</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -12044,10 +11776,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="B136" s="1" t="n">
+        <v>40</v>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
@@ -12135,10 +11865,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
+      <c r="B137" s="2" t="n">
+        <v>304</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
@@ -12214,10 +11942,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="B138" s="1" t="n">
+        <v>38</v>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
@@ -12305,10 +12031,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="B139" s="2" t="n">
+        <v>126</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
@@ -12388,10 +12112,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="B140" s="1" t="n">
+        <v>53</v>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
@@ -12479,10 +12201,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B141" s="1" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="B141" s="1" t="n">
+        <v>50</v>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
@@ -12570,10 +12290,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+      <c r="B142" s="2" t="n">
+        <v>174</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
@@ -12653,10 +12371,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
+      <c r="B143" s="1" t="n">
+        <v>247</v>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
@@ -12744,10 +12460,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B144" s="1" t="n">
+        <v>13</v>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
@@ -12835,10 +12549,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="B145" s="2" t="n">
+        <v>28</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
@@ -12918,10 +12630,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+      <c r="B146" s="1" t="n">
+        <v>210</v>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
@@ -13009,10 +12719,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B147" s="1" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="B147" s="1" t="n">
+        <v>122</v>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
@@ -13100,10 +12808,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B148" s="1" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="B148" s="1" t="n">
+        <v>228</v>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
@@ -13187,10 +12893,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B149" s="1" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
+      <c r="B149" s="1" t="n">
+        <v>212</v>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
@@ -13278,10 +12982,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B150" s="1" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
+      <c r="B150" s="1" t="n">
+        <v>191</v>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
@@ -13369,10 +13071,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B151" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="B151" s="1" t="n">
+        <v>214</v>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
@@ -13460,10 +13160,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="B152" s="2" t="n">
+        <v>92</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
@@ -13543,10 +13241,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B153" s="1" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="B153" s="1" t="n">
+        <v>131</v>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
@@ -13630,10 +13326,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
+      <c r="B154" s="1" t="n">
+        <v>312</v>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
@@ -13721,10 +13415,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
+      <c r="B155" s="2" t="n">
+        <v>237</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
@@ -13804,10 +13496,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+      <c r="B156" s="2" t="n">
+        <v>129</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
@@ -13887,10 +13577,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B157" s="1" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
+      <c r="B157" s="1" t="n">
+        <v>172</v>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
@@ -13978,10 +13666,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B158" s="1" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="B158" s="1" t="n">
+        <v>56</v>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
@@ -14069,10 +13755,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B159" s="1" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+      <c r="B159" s="1" t="n">
+        <v>260</v>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
@@ -14160,10 +13844,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B160" s="1" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="B160" s="1" t="n">
+        <v>25</v>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
@@ -14251,10 +13933,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="B161" s="1" t="n">
+        <v>109</v>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
@@ -14342,10 +14022,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B162" s="1" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="B162" s="1" t="n">
+        <v>156</v>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
@@ -14433,10 +14111,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B163" s="1" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
+      <c r="B163" s="1" t="n">
+        <v>292</v>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
@@ -14520,10 +14196,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B164" s="1" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
+      <c r="B164" s="1" t="n">
+        <v>313</v>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
@@ -14607,10 +14281,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B165" s="1" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
+      <c r="B165" s="1" t="n">
+        <v>182</v>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
@@ -14698,10 +14370,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B166" s="1" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
+      <c r="B166" s="1" t="n">
+        <v>215</v>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
@@ -14789,10 +14459,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B167" s="1" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="B167" s="1" t="n">
+        <v>51</v>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
@@ -14880,10 +14548,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="B168" s="2" t="n">
+        <v>157</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
@@ -14963,10 +14629,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B169" s="1" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
+      <c r="B169" s="1" t="n">
+        <v>336</v>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
@@ -15050,10 +14714,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B170" s="1" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
+      <c r="B170" s="1" t="n">
+        <v>335</v>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
@@ -15137,10 +14799,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B171" s="1" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="B171" s="1" t="n">
+        <v>19</v>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
@@ -15228,10 +14888,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B172" s="1" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="B172" s="1" t="n">
+        <v>108</v>
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
@@ -15319,10 +14977,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B173" s="1" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
+      <c r="B173" s="1" t="n">
+        <v>325</v>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
@@ -15406,10 +15062,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B174" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="B174" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
@@ -15497,10 +15151,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B175" s="1" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="B175" s="1" t="n">
+        <v>26</v>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
@@ -15588,10 +15240,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B176" s="1" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+      <c r="B176" s="1" t="n">
+        <v>279</v>
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
@@ -15679,10 +15329,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B177" s="1" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
+      <c r="B177" s="1" t="n">
+        <v>197</v>
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
@@ -15770,10 +15418,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B178" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
+      <c r="B178" s="1" t="n">
+        <v>201</v>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
@@ -15861,10 +15507,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B179" s="1" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B179" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
@@ -15952,10 +15596,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
+      <c r="B180" s="2" t="n">
+        <v>344</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
@@ -16031,10 +15673,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B181" s="1" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="B181" s="1" t="n">
+        <v>118</v>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
@@ -16122,10 +15762,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
+      <c r="B182" s="2" t="n">
+        <v>306</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
@@ -16205,10 +15843,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="B183" s="2" t="n">
+        <v>134</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
@@ -16288,10 +15924,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B184" s="1" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="B184" s="1" t="n">
+        <v>78</v>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
@@ -16379,10 +16013,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="B185" s="2" t="n">
+        <v>163</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
@@ -16462,10 +16094,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B186" s="1" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="B186" s="1" t="n">
+        <v>165</v>
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
@@ -16553,10 +16183,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B187" s="1" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="B187" s="1" t="n">
+        <v>49</v>
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
@@ -16644,10 +16272,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B188" s="1" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
+      <c r="B188" s="1" t="n">
+        <v>347</v>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
@@ -16731,10 +16357,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+      <c r="B189" s="2" t="n">
+        <v>203</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
@@ -16814,10 +16438,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B190" s="1" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="B190" s="1" t="n">
+        <v>46</v>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
@@ -16905,10 +16527,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B191" s="1" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="B191" s="1" t="n">
+        <v>45</v>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
@@ -16996,10 +16616,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B192" s="1" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="B192" s="1" t="n">
+        <v>39</v>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
@@ -17087,10 +16705,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
+      <c r="B193" s="2" t="n">
+        <v>178</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
@@ -17170,10 +16786,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B194" s="1" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="B194" s="1" t="n">
+        <v>37</v>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
@@ -17261,10 +16875,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B195" s="1" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
+      <c r="B195" s="1" t="n">
+        <v>221</v>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
@@ -17352,10 +16964,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="B196" s="2" t="n">
+        <v>42</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
@@ -17435,10 +17045,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="B197" s="2" t="n">
+        <v>43</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
@@ -17518,10 +17126,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B198" s="1" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="B198" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
@@ -17609,10 +17215,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="B199" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
@@ -17692,10 +17296,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="B200" s="2" t="n">
+        <v>300</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
@@ -17775,10 +17377,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B201" s="1" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="B201" s="1" t="n">
+        <v>150</v>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
@@ -17866,10 +17466,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="B202" s="2" t="n">
+        <v>220</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
@@ -17945,10 +17543,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B203" s="1" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="B203" s="1" t="n">
+        <v>161</v>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
@@ -18036,10 +17632,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="B204" s="2" t="n">
+        <v>101</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
@@ -18115,10 +17709,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B205" s="1" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="B205" s="1" t="n">
+        <v>155</v>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
@@ -18206,10 +17798,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
+      <c r="B206" s="2" t="n">
+        <v>314</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
@@ -18289,10 +17879,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B207" s="1" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="B207" s="1" t="n">
+        <v>111</v>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
@@ -18380,10 +17968,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B208" s="1" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="B208" s="1" t="n">
+        <v>88</v>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
@@ -18471,10 +18057,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B209" s="1" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
+      <c r="B209" s="1" t="n">
+        <v>251</v>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
@@ -18562,10 +18146,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
+      <c r="B210" s="2" t="n">
+        <v>280</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
@@ -18645,10 +18227,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="B211" s="2" t="n">
+        <v>85</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
@@ -18728,10 +18308,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="B212" s="2" t="n">
+        <v>81</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
@@ -18811,10 +18389,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B213" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B213" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
@@ -18902,10 +18478,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B214" s="1" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B214" s="1" t="n">
+        <v>11</v>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
@@ -18993,10 +18567,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B215" s="1" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
+      <c r="B215" s="1" t="n">
+        <v>301</v>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
@@ -19080,10 +18652,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
+      <c r="B216" s="2" t="n">
+        <v>217</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
@@ -19163,10 +18733,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
+      <c r="B217" s="2" t="n">
+        <v>198</v>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
@@ -19246,10 +18814,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="B218" s="2" t="n">
+        <v>119</v>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
@@ -19329,10 +18895,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="B219" s="2" t="n">
+        <v>117</v>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
@@ -19412,10 +18976,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+      <c r="B220" s="2" t="n">
+        <v>175</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
@@ -19495,10 +19057,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
+      <c r="B221" s="2" t="n">
+        <v>187</v>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
@@ -19574,10 +19134,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B222" s="1" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="B222" s="1" t="n">
+        <v>127</v>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
@@ -19665,10 +19223,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+      <c r="B223" s="2" t="n">
+        <v>180</v>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
@@ -19748,10 +19304,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
+      <c r="B224" s="2" t="n">
+        <v>261</v>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
@@ -19831,10 +19385,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B225" s="1" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
+      <c r="B225" s="1" t="n">
+        <v>241</v>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
@@ -19922,10 +19474,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B226" s="1" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="B226" s="1" t="n">
+        <v>95</v>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
@@ -20013,10 +19563,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
+      <c r="B227" s="2" t="n">
+        <v>183</v>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
@@ -20096,10 +19644,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B228" s="1" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B228" s="1" t="n">
+        <v>14</v>
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
@@ -20187,10 +19733,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="B229" s="2" t="n">
+        <v>87</v>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
@@ -20270,10 +19814,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B230" s="1" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
+      <c r="B230" s="1" t="n">
+        <v>211</v>
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
@@ -20361,10 +19903,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B231" s="1" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="B231" s="1" t="n">
+        <v>270</v>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
@@ -20452,10 +19992,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B232" s="1" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="B232" s="1" t="n">
+        <v>345</v>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
@@ -20543,10 +20081,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
+      <c r="B233" s="2" t="n">
+        <v>275</v>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
@@ -20626,10 +20162,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
+      <c r="B234" s="2" t="n">
+        <v>259</v>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
@@ -20709,10 +20243,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
+      <c r="B235" s="2" t="n">
+        <v>245</v>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
@@ -20792,10 +20324,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
+      <c r="B236" s="2" t="n">
+        <v>272</v>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
@@ -20875,10 +20405,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B237" s="1" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="B237" s="1" t="n">
+        <v>90</v>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
@@ -20966,10 +20494,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B238" s="1" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B238" s="1" t="n">
+        <v>12</v>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
@@ -21053,10 +20579,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
+      <c r="B239" s="2" t="n">
+        <v>284</v>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
@@ -21132,10 +20656,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B240" s="1" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
+      <c r="B240" s="1" t="n">
+        <v>288</v>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
@@ -21223,10 +20745,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B241" s="1" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="B241" s="1" t="n">
+        <v>100</v>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
@@ -21314,10 +20834,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B242" s="1" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
+      <c r="B242" s="1" t="n">
+        <v>265</v>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
@@ -21397,10 +20915,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B243" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B243" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
@@ -21488,10 +21004,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B244" s="1" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
+      <c r="B244" s="1" t="n">
+        <v>290</v>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
@@ -21575,10 +21089,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B245" s="1" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
+      <c r="B245" s="1" t="n">
+        <v>326</v>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
@@ -21662,10 +21174,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B246" s="1" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
+      <c r="B246" s="1" t="n">
+        <v>324</v>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
@@ -21753,10 +21263,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B247" s="1" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="B247" s="1" t="n">
+        <v>54</v>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
@@ -21844,10 +21352,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
+      <c r="B248" s="2" t="n">
+        <v>302</v>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
@@ -21927,10 +21433,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="B249" s="2" t="n">
+        <v>159</v>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
@@ -22010,10 +21514,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="B250" s="2" t="n">
+        <v>256</v>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
@@ -22093,10 +21595,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="B251" s="2" t="n">
+        <v>147</v>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
@@ -22176,10 +21676,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
+      <c r="B252" s="2" t="n">
+        <v>337</v>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
@@ -22255,10 +21753,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="B253" s="2" t="n">
+        <v>113</v>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
@@ -22338,10 +21834,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B254" s="1" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
+      <c r="B254" s="1" t="n">
+        <v>315</v>
       </c>
       <c r="C254" s="1" t="inlineStr">
         <is>
@@ -22429,10 +21923,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B255" s="1" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
+      <c r="B255" s="1" t="n">
+        <v>316</v>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
@@ -22520,10 +22012,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
+      <c r="B256" s="2" t="n">
+        <v>352</v>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
@@ -22599,10 +22089,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
+      <c r="B257" s="2" t="n">
+        <v>351</v>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
@@ -22682,10 +22170,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B258" s="1" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
+      <c r="B258" s="1" t="n">
+        <v>235</v>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
@@ -22773,10 +22259,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B259" s="1" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
+      <c r="B259" s="1" t="n">
+        <v>193</v>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
@@ -22864,10 +22348,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B260" s="1" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="B260" s="1" t="n">
+        <v>97</v>
       </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
@@ -22955,10 +22437,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
+      <c r="B261" s="2" t="n">
+        <v>184</v>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
@@ -23038,10 +22518,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B262" s="1" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="B262" s="1" t="n">
+        <v>105</v>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
@@ -23129,10 +22607,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B263" s="1" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
+      <c r="B263" s="1" t="n">
+        <v>196</v>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
@@ -23220,10 +22696,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B264" s="1" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="B264" s="1" t="n">
+        <v>152</v>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
@@ -23311,10 +22785,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B265" s="1" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="B265" s="1" t="n">
+        <v>114</v>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
@@ -23402,10 +22874,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B266" s="1" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
+      <c r="B266" s="1" t="n">
+        <v>199</v>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
@@ -23493,10 +22963,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B267" s="1" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="B267" s="1" t="n">
+        <v>89</v>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
@@ -23584,10 +23052,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B268" s="1" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="B268" s="1" t="n">
+        <v>69</v>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
@@ -23675,10 +23141,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B269" s="1" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
+      <c r="B269" s="1" t="n">
+        <v>227</v>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
@@ -23766,10 +23230,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B270" s="1" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="B270" s="1" t="n">
+        <v>79</v>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
@@ -23857,10 +23319,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B271" s="1" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
+      <c r="B271" s="1" t="n">
+        <v>208</v>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
@@ -23948,10 +23408,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B272" s="1" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="B272" s="1" t="n">
+        <v>47</v>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
@@ -24039,10 +23497,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B273" s="1" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="B273" s="1" t="n">
+        <v>173</v>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
@@ -24130,10 +23586,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
+      <c r="B274" s="2" t="n">
+        <v>226</v>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
@@ -24213,10 +23667,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="B275" s="2" t="n">
+        <v>41</v>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
@@ -24296,10 +23748,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B276" s="1" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
+      <c r="B276" s="1" t="n">
+        <v>254</v>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
@@ -24383,10 +23833,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="B277" s="2" t="n">
+        <v>146</v>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
@@ -24466,10 +23914,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="B278" s="2" t="n">
+        <v>93</v>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
@@ -24549,10 +23995,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B279" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
+      <c r="B279" s="2" t="n">
+        <v>135</v>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
@@ -24632,10 +24076,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B280" s="1" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
+      <c r="B280" s="1" t="n">
+        <v>242</v>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
@@ -24723,10 +24165,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B281" s="1" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
+      <c r="B281" s="1" t="n">
+        <v>297</v>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
@@ -24814,10 +24254,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
+      <c r="B282" s="2" t="n">
+        <v>236</v>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
@@ -24897,10 +24335,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B283" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="B283" s="2" t="n">
+        <v>128</v>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
@@ -24980,10 +24416,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B284" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="B284" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
@@ -25071,10 +24505,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
+      <c r="B285" s="2" t="n">
+        <v>225</v>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
@@ -25154,10 +24586,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="B286" s="2" t="n">
+        <v>121</v>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
@@ -25237,10 +24667,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B287" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
+      <c r="B287" s="2" t="n">
+        <v>271</v>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
@@ -25320,10 +24748,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B288" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="B288" s="2" t="n">
+        <v>230</v>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
@@ -25403,10 +24829,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B289" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+      <c r="B289" s="2" t="n">
+        <v>102</v>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
@@ -25486,10 +24910,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B290" s="1" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="B290" s="1" t="n">
+        <v>104</v>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
@@ -25577,10 +24999,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B291" s="1" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="B291" s="1" t="n">
+        <v>103</v>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
@@ -25668,10 +25088,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B292" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+      <c r="B292" s="2" t="n">
+        <v>266</v>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
@@ -25751,10 +25169,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B293" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="B293" s="2" t="n">
+        <v>133</v>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
@@ -25834,10 +25250,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B294" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="B294" s="2" t="n">
+        <v>64</v>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
@@ -25917,10 +25331,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B295" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="B295" s="2" t="n">
+        <v>63</v>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
@@ -26000,10 +25412,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B296" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="B296" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
@@ -26083,10 +25493,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B297" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="B297" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
@@ -26166,10 +25574,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B298" s="1" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="B298" s="1" t="n">
+        <v>130</v>
       </c>
       <c r="C298" s="1" t="inlineStr">
         <is>
@@ -26253,10 +25659,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B299" s="1" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="B299" s="1" t="n">
+        <v>115</v>
       </c>
       <c r="C299" s="1" t="inlineStr">
         <is>
@@ -26344,10 +25748,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B300" s="1" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
+      <c r="B300" s="1" t="n">
+        <v>305</v>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
@@ -26435,10 +25837,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="B301" s="2" t="n">
+        <v>31</v>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
@@ -26518,10 +25918,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B302" s="1" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="B302" s="1" t="n">
+        <v>160</v>
       </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
@@ -26609,10 +26007,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B303" s="1" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="B303" s="1" t="n">
+        <v>48</v>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
@@ -26700,10 +26096,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B304" s="1" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
+      <c r="B304" s="1" t="n">
+        <v>233</v>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
@@ -26791,10 +26185,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B305" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
@@ -26874,10 +26266,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B306" s="1" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="B306" s="1" t="n">
+        <v>21</v>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
@@ -26965,10 +26355,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B307" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
@@ -27044,10 +26432,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
+      <c r="B308" s="2" t="n">
+        <v>281</v>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
@@ -27123,10 +26509,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B309" s="1" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="B309" s="1" t="n">
+        <v>32</v>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
@@ -27214,10 +26598,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B310" s="1" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
+      <c r="B310" s="1" t="n">
+        <v>239</v>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
@@ -27305,10 +26687,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B311" s="1" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="B311" s="1" t="n">
+        <v>33</v>
       </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
@@ -27396,10 +26776,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B312" s="1" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
+      <c r="B312" s="1" t="n">
+        <v>205</v>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
@@ -27487,10 +26865,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B313" s="1" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="B313" s="1" t="n">
+        <v>124</v>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
@@ -27578,10 +26954,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B314" s="2" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
+      <c r="B314" s="2" t="n">
+        <v>355</v>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
@@ -27657,10 +27031,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B315" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
+      <c r="B315" s="2" t="n">
+        <v>287</v>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
@@ -27740,10 +27112,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B316" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
+      <c r="B316" s="2" t="n">
+        <v>322</v>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
@@ -27823,10 +27193,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B317" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
+      <c r="B317" s="2" t="n">
+        <v>323</v>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
@@ -27906,10 +27274,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B318" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="B318" s="2" t="n">
+        <v>258</v>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
@@ -27989,10 +27355,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B319" s="1" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="B319" s="1" t="n">
+        <v>116</v>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
@@ -28080,10 +27444,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B320" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
+      <c r="B320" s="2" t="n">
+        <v>186</v>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
@@ -28163,10 +27525,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B321" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
+      <c r="B321" s="2" t="n">
+        <v>341</v>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
@@ -28246,10 +27606,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B322" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="B322" s="2" t="n">
+        <v>71</v>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
@@ -28329,10 +27687,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B323" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="B323" s="2" t="n">
+        <v>136</v>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
@@ -28412,10 +27768,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B324" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="B324" s="2" t="n">
+        <v>189</v>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
@@ -28495,10 +27849,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B325" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
+      <c r="B325" s="2" t="n">
+        <v>340</v>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
@@ -28578,10 +27930,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B326" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B326" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
@@ -28661,10 +28011,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B327" s="1" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="B327" s="1" t="n">
+        <v>200</v>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
@@ -28752,10 +28100,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B328" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="B328" s="2" t="n">
+        <v>67</v>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
@@ -28835,10 +28181,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B329" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="B329" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
@@ -28918,10 +28262,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B330" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
+      <c r="B330" s="2" t="n">
+        <v>229</v>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
@@ -29001,10 +28343,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B331" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
+      <c r="B331" s="2" t="n">
+        <v>283</v>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
@@ -29084,10 +28424,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B332" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
+      <c r="B332" s="2" t="n">
+        <v>307</v>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
@@ -29167,10 +28505,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B333" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
+      <c r="B333" s="2" t="n">
+        <v>185</v>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
@@ -29250,10 +28586,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B334" s="1" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="B334" s="1" t="n">
+        <v>112</v>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
@@ -29341,10 +28675,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B335" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
+      <c r="B335" s="2" t="n">
+        <v>181</v>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
@@ -29424,10 +28756,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B336" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+      <c r="B336" s="2" t="n">
+        <v>299</v>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
@@ -29507,10 +28837,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B337" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="B337" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
@@ -29590,10 +28918,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B338" s="1" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B338" s="1" t="n">
+        <v>123</v>
       </c>
       <c r="C338" s="1" t="inlineStr">
         <is>
@@ -29681,10 +29007,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B339" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+      <c r="B339" s="2" t="n">
+        <v>350</v>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
@@ -29760,10 +29084,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B340" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+      <c r="B340" s="2" t="n">
+        <v>213</v>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
@@ -29843,10 +29165,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B341" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="B341" s="2" t="n">
+        <v>240</v>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
@@ -29926,10 +29246,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B342" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
+      <c r="B342" s="2" t="n">
+        <v>153</v>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
@@ -30009,10 +29327,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B343" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
+      <c r="B343" s="2" t="n">
+        <v>246</v>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
@@ -30092,10 +29408,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B344" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="B344" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
@@ -30175,10 +29489,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B345" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="B345" s="2" t="n">
+        <v>44</v>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
@@ -30258,10 +29570,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B346" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
+      <c r="B346" s="2" t="n">
+        <v>329</v>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
@@ -30341,10 +29651,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B347" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="B347" s="2" t="n">
+        <v>52</v>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
@@ -30424,10 +29732,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B348" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="B348" s="2" t="n">
+        <v>120</v>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
@@ -30507,10 +29813,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B349" s="1" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
+      <c r="B349" s="1" t="n">
+        <v>232</v>
       </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
@@ -30598,10 +29902,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B350" s="1" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
+      <c r="B350" s="1" t="n">
+        <v>234</v>
       </c>
       <c r="C350" s="1" t="inlineStr">
         <is>
@@ -30689,10 +29991,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B351" s="1" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
+      <c r="B351" s="1" t="n">
+        <v>231</v>
       </c>
       <c r="C351" s="1" t="inlineStr">
         <is>
@@ -30780,10 +30080,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B352" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
+      <c r="B352" s="2" t="n">
+        <v>209</v>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
@@ -30863,10 +30161,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B353" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
+      <c r="B353" s="2" t="n">
+        <v>346</v>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
@@ -30942,10 +30238,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B354" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="B354" s="2" t="n">
+        <v>142</v>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
@@ -31025,10 +30319,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B355" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B355" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
@@ -31104,10 +30396,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B356" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="B356" s="2" t="n">
+        <v>141</v>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
@@ -31187,10 +30477,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B357" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B357" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
@@ -31266,10 +30554,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B358" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
+      <c r="B358" s="2" t="n">
+        <v>354</v>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
@@ -31349,10 +30635,8 @@
           <t>CIJEPANO</t>
         </is>
       </c>
-      <c r="B359" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B359" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
@@ -41222,10 +40506,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>360</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -41305,10 +40587,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>386</v>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
@@ -41392,10 +40672,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>358</v>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
@@ -41483,10 +40761,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>391</v>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
@@ -41570,10 +40846,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
+      <c r="B6" s="1" t="n">
+        <v>392</v>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
@@ -41657,10 +40931,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>378</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
@@ -41744,10 +41016,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
+      <c r="B8" s="2" t="n">
+        <v>397</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -41823,10 +41093,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
+      <c r="B9" s="2" t="n">
+        <v>374</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -41902,10 +41170,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
+      <c r="B10" s="1" t="n">
+        <v>396</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
@@ -41989,10 +41255,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
+      <c r="B11" s="1" t="n">
+        <v>396</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -42076,10 +41340,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
+      <c r="B12" s="2" t="n">
+        <v>387</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -42155,10 +41417,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
+      <c r="B13" s="2" t="n">
+        <v>382</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -42234,10 +41494,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="B14" s="2" t="n">
+        <v>393</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -42313,10 +41571,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
+      <c r="B15" s="1" t="n">
+        <v>370</v>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
@@ -42400,10 +41656,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
+      <c r="B16" s="1" t="n">
+        <v>370</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
@@ -42487,10 +41741,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
+      <c r="B17" s="2" t="n">
+        <v>362</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -42566,10 +41818,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
+      <c r="B18" s="1" t="n">
+        <v>363</v>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
@@ -42653,10 +41903,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
+      <c r="B19" s="1" t="n">
+        <v>363</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
@@ -42740,10 +41988,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
+      <c r="B20" s="1" t="n">
+        <v>375</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
@@ -42827,10 +42073,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
+      <c r="B21" s="1" t="n">
+        <v>395</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
@@ -42914,10 +42158,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
+      <c r="B22" s="1" t="n">
+        <v>369</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
@@ -43001,10 +42243,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
+      <c r="B23" s="1" t="n">
+        <v>359</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
@@ -43092,10 +42332,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
+      <c r="B24" s="1" t="n">
+        <v>383</v>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
@@ -43179,10 +42417,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
+      <c r="B25" s="1" t="n">
+        <v>361</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
@@ -43266,10 +42502,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
+      <c r="B26" s="2" t="n">
+        <v>376</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -43345,10 +42579,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
+      <c r="B27" s="1" t="n">
+        <v>367</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -43432,10 +42664,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
+      <c r="B28" s="1" t="n">
+        <v>368</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
@@ -43519,10 +42749,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
+      <c r="B29" s="2" t="n">
+        <v>388</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -43598,10 +42826,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
+      <c r="B30" s="1" t="n">
+        <v>371</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -43685,10 +42911,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="B31" s="2" t="n">
+        <v>385</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -43764,10 +42988,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
+      <c r="B32" s="1" t="n">
+        <v>366</v>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
@@ -43851,10 +43073,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="B33" s="1" t="n">
+        <v>390</v>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
@@ -43938,10 +43158,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+      <c r="B34" s="1" t="n">
+        <v>389</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -44025,10 +43243,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
+      <c r="B35" s="2" t="n">
+        <v>377</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -44104,10 +43320,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+      <c r="B36" s="2" t="n">
+        <v>379</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -44183,10 +43397,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
+      <c r="B37" s="2" t="n">
+        <v>381</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -44262,10 +43474,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
+      <c r="B38" s="2" t="n">
+        <v>380</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -44337,10 +43547,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
+      <c r="B39" s="2" t="n">
+        <v>372</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -44416,10 +43624,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
+      <c r="B40" s="1" t="n">
+        <v>373</v>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
@@ -44503,10 +43709,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
+      <c r="B41" s="2" t="n">
+        <v>398</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -44582,10 +43786,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
+      <c r="B42" s="1" t="n">
+        <v>394</v>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
@@ -44669,10 +43871,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
+      <c r="B43" s="2" t="n">
+        <v>364</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -44748,10 +43948,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
+      <c r="B44" s="2" t="n">
+        <v>365</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
@@ -44827,10 +44025,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+      <c r="B45" s="2" t="n">
+        <v>384</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -44906,10 +44102,8 @@
           <t>U DUGOM</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
+      <c r="B46" s="2" t="n">
+        <v>357</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
@@ -46282,10 +45476,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>76</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -46361,10 +45553,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -46440,10 +45630,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -46519,10 +45707,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="B5" s="2" t="n">
+        <v>62</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -46598,10 +45784,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="B6" s="2" t="n">
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -46677,10 +45861,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="B7" s="2" t="n">
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -46756,10 +45938,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="B8" s="2" t="n">
+        <v>83</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -46835,10 +46015,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>32.</t>
-        </is>
+      <c r="B9" s="1" t="n">
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
@@ -46922,10 +46100,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="B10" s="1" t="n">
+        <v>90</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
@@ -47009,10 +46185,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>46.</t>
-        </is>
+      <c r="B11" s="2" t="n">
+        <v>46</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -47088,10 +46262,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19.</t>
-        </is>
+      <c r="B12" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -47167,10 +46339,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>11.</t>
-        </is>
+      <c r="B13" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -47246,10 +46416,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="B14" s="2" t="n">
+        <v>77</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -47325,10 +46493,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="B15" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -47404,10 +46570,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="B16" s="2" t="n">
+        <v>85</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -47483,10 +46647,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>29.</t>
-        </is>
+      <c r="B17" s="1" t="n">
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
@@ -47570,10 +46732,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
+      <c r="B18" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -47653,10 +46813,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>30.</t>
-        </is>
+      <c r="B19" s="1" t="n">
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
@@ -47740,10 +46898,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="B20" s="2" t="n">
+        <v>87</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -47819,10 +46975,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>47.</t>
-        </is>
+      <c r="B21" s="2" t="n">
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -48044,10 +47198,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="B24" s="2" t="n">
+        <v>79</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -48123,10 +47275,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="B25" s="2" t="n">
+        <v>74</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -48202,10 +47352,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="B26" s="2" t="n">
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -48281,10 +47429,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="B27" s="2" t="n">
+        <v>72</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -48360,10 +47506,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>39.</t>
-        </is>
+      <c r="B28" s="2" t="n">
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -48439,10 +47583,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="B29" s="2" t="n">
+        <v>66</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -48518,10 +47660,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
+      <c r="B30" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -48597,10 +47737,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="B31" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -48676,10 +47814,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="B32" s="2" t="n">
+        <v>89</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -48755,10 +47891,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>45.</t>
-        </is>
+      <c r="B33" s="1" t="n">
+        <v>45</v>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
@@ -48842,10 +47976,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>15.</t>
-        </is>
+      <c r="B34" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -48921,10 +48053,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>38.</t>
-        </is>
+      <c r="B35" s="2" t="n">
+        <v>38</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -49000,10 +48130,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="B36" s="2" t="n">
+        <v>67</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -49079,10 +48207,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="B37" s="2" t="n">
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -49158,10 +48284,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>44.</t>
-        </is>
+      <c r="B38" s="2" t="n">
+        <v>44</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -49237,10 +48361,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="B39" s="1" t="n">
+        <v>51</v>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
@@ -49324,10 +48446,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>20.</t>
-        </is>
+      <c r="B40" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -49403,10 +48523,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>12.</t>
-        </is>
+      <c r="B41" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -49482,10 +48600,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="B42" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -49561,10 +48677,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="B43" s="2" t="n">
+        <v>78</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -49640,10 +48754,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="B44" s="1" t="n">
+        <v>49</v>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
@@ -49794,10 +48906,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="B46" s="2" t="n">
+        <v>56</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
@@ -49873,10 +48983,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="B47" s="1" t="n">
+        <v>68</v>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
@@ -49960,10 +49068,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>33.</t>
-        </is>
+      <c r="B48" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -50039,10 +49145,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>13.</t>
-        </is>
+      <c r="B49" s="1" t="n">
+        <v>13</v>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
@@ -50126,10 +49230,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="B50" s="2" t="n">
+        <v>64</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -50205,10 +49307,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>43.</t>
-        </is>
+      <c r="B51" s="2" t="n">
+        <v>43</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -50284,10 +49384,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
+      <c r="B52" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -50367,10 +49465,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28.</t>
-        </is>
+      <c r="B53" s="2" t="n">
+        <v>28</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
@@ -50446,10 +49542,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>42.</t>
-        </is>
+      <c r="B54" s="1" t="n">
+        <v>42</v>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
@@ -50533,10 +49627,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21.</t>
-        </is>
+      <c r="B55" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -50612,10 +49704,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="B56" s="2" t="n">
+        <v>69</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
@@ -50691,10 +49781,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>14.</t>
-        </is>
+      <c r="B57" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -50770,10 +49858,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
+      <c r="B58" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
@@ -50928,10 +50014,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
+      <c r="B60" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
@@ -51019,10 +50103,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="B61" s="2" t="n">
+        <v>91</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
@@ -51098,10 +50180,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>10.</t>
-        </is>
+      <c r="B62" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
@@ -51185,10 +50265,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24.</t>
-        </is>
+      <c r="B63" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
@@ -51264,10 +50342,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="B64" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
@@ -51343,10 +50419,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="B65" s="1" t="n">
+        <v>70</v>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
@@ -51430,10 +50504,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>35.</t>
-        </is>
+      <c r="B66" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
@@ -51509,10 +50581,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>16.</t>
-        </is>
+      <c r="B67" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
@@ -51596,10 +50666,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>23.</t>
-        </is>
+      <c r="B68" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
@@ -51675,10 +50743,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>34.</t>
-        </is>
+      <c r="B69" s="2" t="n">
+        <v>34</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
@@ -51754,10 +50820,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="B70" s="2" t="n">
+        <v>71</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
@@ -51833,10 +50897,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="B71" s="2" t="n">
+        <v>57</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
@@ -51912,10 +50974,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18.</t>
-        </is>
+      <c r="B72" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -51991,10 +51051,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
+      <c r="B73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
@@ -52074,10 +51132,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>8.</t>
-        </is>
+      <c r="B74" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -52157,10 +51213,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="B75" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
@@ -52236,10 +51290,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="B76" s="2" t="n">
+        <v>75</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
@@ -52315,10 +51367,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="B77" s="2" t="n">
+        <v>92</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
@@ -52394,10 +51444,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="B78" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -52473,10 +51521,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>22.</t>
-        </is>
+      <c r="B79" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
@@ -52552,10 +51598,8 @@
           <t>RVI</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="B80" s="2" t="n">
+        <v>82</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
@@ -54408,10 +53452,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -54487,10 +53529,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -54566,10 +53606,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -54649,10 +53687,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -54728,10 +53764,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="B6" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -54807,10 +53841,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B7" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -54890,10 +53922,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="B8" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -54969,10 +53999,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="B9" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -55052,10 +54080,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="B10" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -55131,10 +54157,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="B11" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -55210,10 +54234,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -55293,10 +54315,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="B13" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -55376,10 +54396,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B14" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -55455,10 +54473,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="B15" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -55534,10 +54550,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B16" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -55613,10 +54627,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B17" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -55692,10 +54704,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="B18" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -55771,10 +54781,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B19" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -55850,10 +54858,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="B20" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -55929,10 +54935,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B21" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -56012,10 +55016,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="B22" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -56095,10 +55097,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B23" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -56174,10 +55174,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B24" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -56253,10 +55251,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="B25" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -56336,10 +55332,8 @@
           <t>PORODICE ŠEHIDA</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B26" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -57432,10 +56426,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="1" t="inlineStr">
@@ -57507,10 +56499,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="1" t="inlineStr">
@@ -57582,10 +56572,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
@@ -57649,10 +56637,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="inlineStr"/>
       <c r="D5" s="1" t="inlineStr">
@@ -57724,10 +56710,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B6" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
@@ -57791,10 +56775,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
@@ -57866,10 +56848,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B8" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
@@ -57933,10 +56913,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="B9" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
@@ -58000,10 +56978,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="B10" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
@@ -58071,10 +57047,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="B11" s="2" t="n">
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
@@ -58146,10 +57120,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B12" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
@@ -58213,10 +57185,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B13" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
@@ -58280,10 +57250,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="B14" s="1" t="n">
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="inlineStr"/>
       <c r="D14" s="1" t="inlineStr">
@@ -58355,10 +57323,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="B15" s="1" t="n">
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="inlineStr"/>
       <c r="D15" s="1" t="inlineStr">
@@ -58430,10 +57396,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="B16" s="1" t="n">
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="inlineStr"/>
       <c r="D16" s="1" t="inlineStr">
@@ -58505,10 +57469,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="B17" s="1" t="n">
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="inlineStr"/>
       <c r="D17" s="1" t="inlineStr">
@@ -58580,10 +57542,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="B18" s="2" t="n">
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
@@ -58655,10 +57615,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="B19" s="1" t="n">
+        <v>37</v>
       </c>
       <c r="C19" s="1" t="inlineStr"/>
       <c r="D19" s="1" t="inlineStr">
@@ -58730,10 +57688,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B20" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
@@ -58797,10 +57753,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="B21" s="2" t="n">
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
@@ -58868,10 +57822,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="B22" s="2" t="n">
+        <v>38</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
@@ -58935,10 +57887,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="B23" s="1" t="n">
+        <v>39</v>
       </c>
       <c r="C23" s="1" t="inlineStr"/>
       <c r="D23" s="1" t="inlineStr">
@@ -59010,10 +57960,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="B24" s="1" t="n">
+        <v>40</v>
       </c>
       <c r="C24" s="1" t="inlineStr"/>
       <c r="D24" s="1" t="inlineStr">
@@ -59085,10 +58033,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="B25" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
@@ -59152,10 +58098,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="B26" s="1" t="n">
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="inlineStr"/>
       <c r="D26" s="1" t="inlineStr">
@@ -59227,10 +58171,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="B27" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="C27" s="1" t="inlineStr"/>
       <c r="D27" s="1" t="inlineStr">
@@ -59302,10 +58244,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B28" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
@@ -59369,10 +58309,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="B29" s="1" t="n">
+        <v>41</v>
       </c>
       <c r="C29" s="1" t="inlineStr"/>
       <c r="D29" s="1" t="inlineStr">
@@ -59444,10 +58382,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="B30" s="1" t="n">
+        <v>58</v>
       </c>
       <c r="C30" s="1" t="inlineStr"/>
       <c r="D30" s="1" t="inlineStr">
@@ -59519,10 +58455,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="B31" s="1" t="n">
+        <v>59</v>
       </c>
       <c r="C31" s="1" t="inlineStr"/>
       <c r="D31" s="1" t="inlineStr">
@@ -59594,10 +58528,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B32" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
@@ -59661,10 +58593,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B33" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
@@ -59728,10 +58658,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="B34" s="2" t="n">
+        <v>42</v>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
@@ -59795,10 +58723,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="B35" s="1" t="n">
+        <v>43</v>
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="1" t="inlineStr">
@@ -59870,10 +58796,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B36" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
@@ -59937,10 +58861,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B37" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
@@ -60004,10 +58926,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="B38" s="1" t="n">
+        <v>15</v>
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="1" t="inlineStr">
@@ -60079,10 +58999,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="B39" s="1" t="n">
+        <v>44</v>
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="1" t="inlineStr">
@@ -60154,10 +59072,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="B40" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
@@ -60221,10 +59137,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="B41" s="1" t="n">
+        <v>45</v>
       </c>
       <c r="C41" s="1" t="inlineStr"/>
       <c r="D41" s="1" t="inlineStr">
@@ -60296,10 +59210,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="B42" s="1" t="n">
+        <v>46</v>
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="1" t="inlineStr">
@@ -60371,10 +59283,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="B43" s="2" t="n">
+        <v>47</v>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
@@ -60438,10 +59348,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="B44" s="2" t="n">
+        <v>48</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
@@ -60505,10 +59413,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="B45" s="2" t="n">
+        <v>49</v>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
@@ -60572,10 +59478,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="B46" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
@@ -60639,10 +59543,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="B47" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
@@ -60706,10 +59608,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="B48" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
@@ -60773,10 +59673,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="B49" s="1" t="n">
+        <v>51</v>
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="1" t="inlineStr">
@@ -60852,10 +59750,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="B50" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr">
@@ -60927,10 +59823,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="B51" s="1" t="n">
+        <v>56</v>
       </c>
       <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="1" t="inlineStr">
@@ -61002,10 +59896,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="B52" s="2" t="n">
+        <v>29</v>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
@@ -61073,10 +59965,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="B53" s="1" t="n">
+        <v>57</v>
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="1" t="inlineStr">
@@ -61148,10 +60038,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="B54" s="1" t="n">
+        <v>23</v>
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="1" t="inlineStr">
@@ -61223,10 +60111,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B55" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
@@ -61290,10 +60176,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="B56" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
@@ -61357,10 +60241,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="B57" s="1" t="n">
+        <v>53</v>
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="1" t="inlineStr">
@@ -61432,10 +60314,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="B58" s="2" t="n">
+        <v>54</v>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
@@ -61499,10 +60379,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="B59" s="1" t="n">
+        <v>62</v>
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="1" t="inlineStr">
@@ -61578,10 +60456,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="B60" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="1" t="inlineStr">
@@ -61653,10 +60529,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="B61" s="1" t="n">
+        <v>52</v>
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="1" t="inlineStr">
@@ -61728,10 +60602,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="B62" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
@@ -61795,10 +60667,8 @@
           <t>SINDIKAT</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="B63" s="2" t="n">
+        <v>31</v>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
